--- a/data/trans_camb/IP1014-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Habitat-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,36</t>
+          <t>-0,88; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,48</t>
+          <t>-0,23; 1,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,83</t>
+          <t>-1,39; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,72</t>
+          <t>-1,08; 1,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,4</t>
+          <t>-0,98; 0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,63</t>
+          <t>-0,85; 0,64</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,79</t>
+          <t>-1,29; 0,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,76</t>
+          <t>-0,67; 0,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,11; 0,0</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,32</t>
+          <t>-0,34; 2,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,15</t>
+          <t>-0,19; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,0</t>
+          <t>-1,01; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,53</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,55; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,74</t>
+          <t>-0,48; 0,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,28</t>
+          <t>-0,77; 0,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,46</t>
+          <t>-0,21; 0,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 393,76</t>
+          <t>-65,31; 392,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 223,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 341,17</t>
+          <t>-59,76; 329,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,91</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Habitat-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,35</t>
+          <t>-0,9; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,68</t>
+          <t>-0,23; 1,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,0</t>
+          <t>-1,26; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,86</t>
+          <t>-1,42; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,75</t>
+          <t>-1,09; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,39</t>
+          <t>-1,17; 0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,64</t>
+          <t>-0,84; 0,64</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,8</t>
+          <t>-1,32; 0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,75</t>
+          <t>-0,53; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,0</t>
+          <t>-1,23; 0,0</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,56</t>
+          <t>-0,34; 2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-1,9; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,12</t>
+          <t>-0,18; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-1,15; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,74</t>
+          <t>-0,44; 0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,24</t>
+          <t>-0,86; 0,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,48</t>
+          <t>-0,2; 0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,09</t>
+          <t>-0,45; 0,12</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 392,31</t>
+          <t>-67,96; 474,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,56</t>
+          <t>-100,0; 206,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 329,97</t>
+          <t>-55,86; 368,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 234,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>-1,3; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,38</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,47</t>
+          <t>-0,38; 1,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,0</t>
+          <t>-1,16; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,33</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,4; 0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,0</t>
+          <t>-1,0; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,04</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,69</t>
+          <t>-1,32; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,32</t>
+          <t>-0,99; 0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,64</t>
+          <t>-0,84; 0,63</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-14,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-14,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>-1,63; 0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,79</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,8</t>
+          <t>-0,49; 0,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,0</t>
+          <t>-1,12; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-8,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-8,19%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,37; 2,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,12</t>
+          <t>-0,18; 1,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,0</t>
+          <t>-0,92; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>201,7%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>201,7%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,57</t>
+          <t>-0,47; 0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,0</t>
+          <t>-0,75; 0,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,79</t>
+          <t>-0,16; 0,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,24</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,54</t>
+          <t>-0,26; 0,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,12</t>
+          <t>-0,48; 0,09</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,06%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>100,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-43,06%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,48; 393,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 474,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 206,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 368,82</t>
+          <t>-55,95; 341,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,5</t>
+          <t>-100,0; 105,91</t>
         </is>
       </c>
     </row>
